--- a/data/trans_orig/Q64C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q64C-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas que trabaja a la semana</t>
+          <t>Número medio de horas que trabaja a la semana (tasa de respuesta: 97,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,64; 41,16</t>
+          <t>37,59; 41,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,2; 42,05</t>
+          <t>37,16; 41,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,67; 38,64</t>
+          <t>32,83; 38,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,18; 40,88</t>
+          <t>35,07; 40,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,68; 38,62</t>
+          <t>34,77; 38,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,82; 36,13</t>
+          <t>30,92; 36,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,06; 36,74</t>
+          <t>31,97; 36,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,81; 36,44</t>
+          <t>30,43; 36,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,85; 39,54</t>
+          <t>36,92; 39,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34,52; 38,4</t>
+          <t>34,61; 38,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33,37; 36,96</t>
+          <t>33,26; 37,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,12; 38,4</t>
+          <t>34,36; 38,35</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,48; 41,11</t>
+          <t>39,41; 41,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,41; 41,47</t>
+          <t>39,46; 41,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,34; 39,7</t>
+          <t>37,39; 39,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,98; 39,06</t>
+          <t>37,04; 39,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,14; 37,54</t>
+          <t>35,12; 37,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,94; 37,29</t>
+          <t>34,86; 37,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,54; 36,58</t>
+          <t>33,68; 36,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,56; 36,43</t>
+          <t>26,48; 36,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,12; 39,47</t>
+          <t>38,16; 39,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,87; 39,41</t>
+          <t>37,79; 39,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,09; 37,99</t>
+          <t>36,09; 37,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,69; 37,47</t>
+          <t>30,21; 37,49</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,74; 42,59</t>
+          <t>40,68; 42,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,63; 42,4</t>
+          <t>40,58; 42,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,77; 40,78</t>
+          <t>38,65; 40,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38,86; 40,58</t>
+          <t>38,85; 40,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,47; 38,37</t>
+          <t>35,47; 38,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,24; 37,1</t>
+          <t>34,16; 37,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,56; 36,32</t>
+          <t>33,51; 36,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,43; 36,11</t>
+          <t>34,53; 36,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,21; 40,73</t>
+          <t>39,14; 40,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38,37; 39,98</t>
+          <t>38,35; 40,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36,95; 38,63</t>
+          <t>36,88; 38,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,22; 38,46</t>
+          <t>37,22; 38,45</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,8; 42,59</t>
+          <t>40,85; 42,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,77; 42,65</t>
+          <t>40,71; 42,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,12; 41,42</t>
+          <t>39,19; 41,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,16; 40,78</t>
+          <t>16,95; 40,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,09; 42,06</t>
+          <t>38,08; 41,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,83; 37,39</t>
+          <t>34,0; 37,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,36; 36,57</t>
+          <t>33,44; 36,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,61; 36,83</t>
+          <t>34,62; 36,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40,4; 42,11</t>
+          <t>40,25; 41,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38,38; 40,24</t>
+          <t>38,38; 40,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,16; 39,09</t>
+          <t>37,17; 39,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,56; 38,47</t>
+          <t>21,14; 38,46</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,18; 44,11</t>
+          <t>41,21; 44,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,07; 44,45</t>
+          <t>41,06; 44,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,68; 42,15</t>
+          <t>38,77; 42,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39,8; 41,53</t>
+          <t>39,8; 41,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,67; 39,52</t>
+          <t>34,02; 39,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,98; 41,85</t>
+          <t>36,9; 41,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,59; 37,24</t>
+          <t>32,29; 37,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,78; 36,79</t>
+          <t>34,91; 36,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,6; 42,43</t>
+          <t>39,58; 42,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40,41; 43,21</t>
+          <t>40,51; 43,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,02; 39,73</t>
+          <t>36,84; 39,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,01; 39,36</t>
+          <t>38,07; 39,36</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37,05; 41,73</t>
+          <t>37,07; 41,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1446,17 +1446,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,96; 42,06</t>
+          <t>23,21; 42,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,35; 38,51</t>
+          <t>29,56; 38,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,72; 46,11</t>
+          <t>19,72; 45,91</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,61; 40,09</t>
+          <t>23,52; 40,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>34,33; 39,34</t>
+          <t>34,41; 39,41</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>40,69; 41,6</t>
+          <t>40,71; 41,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40,71; 41,75</t>
+          <t>40,76; 41,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38,84; 40,02</t>
+          <t>38,88; 40,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,93; 39,89</t>
+          <t>25,59; 39,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>36,34; 37,83</t>
+          <t>36,41; 37,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,07; 36,69</t>
+          <t>35,06; 36,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,16; 35,67</t>
+          <t>34,18; 35,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,49; 35,82</t>
+          <t>32,33; 35,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39,36; 40,13</t>
+          <t>39,34; 40,16</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38,67; 39,51</t>
+          <t>38,59; 39,51</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36,99; 37,96</t>
+          <t>37,06; 38,02</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,16; 37,84</t>
+          <t>28,34; 37,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q64C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q64C-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38,47</t>
+          <t>38,75</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>33,84</t>
+          <t>33,48</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,35</t>
+          <t>36,31</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,59; 41,29</t>
+          <t>37,62; 41,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,16; 41,9</t>
+          <t>37,27; 42,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,83; 38,78</t>
+          <t>32,79; 38,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,07; 40,77</t>
+          <t>35,61; 41,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,77; 38,56</t>
+          <t>34,73; 38,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,92; 36,03</t>
+          <t>31,14; 36,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,97; 36,56</t>
+          <t>32,2; 36,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,43; 36,45</t>
+          <t>30,5; 36,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,92; 39,53</t>
+          <t>36,83; 39,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34,61; 38,18</t>
+          <t>34,47; 38,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33,26; 37,04</t>
+          <t>33,34; 36,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,36; 38,35</t>
+          <t>34,09; 38,63</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38,19</t>
+          <t>38,56</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,85</t>
+          <t>35,85</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,48</t>
+          <t>37,34</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,41; 41,09</t>
+          <t>39,52; 41,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,46; 41,52</t>
+          <t>39,47; 41,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,39; 39,73</t>
+          <t>37,34; 39,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37,04; 39,09</t>
+          <t>37,44; 39,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,12; 37,73</t>
+          <t>35,14; 37,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,86; 37,23</t>
+          <t>34,88; 37,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,68; 36,62</t>
+          <t>33,7; 36,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,48; 36,34</t>
+          <t>34,62; 36,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,16; 39,51</t>
+          <t>38,11; 39,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,79; 39,39</t>
+          <t>37,84; 39,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,09; 37,92</t>
+          <t>36,12; 37,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,21; 37,49</t>
+          <t>36,53; 38,0</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39,73</t>
+          <t>39,68</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35,39</t>
+          <t>35,47</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37,85</t>
+          <t>37,88</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,68; 42,51</t>
+          <t>40,67; 42,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,58; 42,37</t>
+          <t>40,56; 42,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,65; 40,73</t>
+          <t>38,82; 40,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38,85; 40,51</t>
+          <t>38,82; 40,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,47; 38,48</t>
+          <t>35,49; 38,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,16; 37,02</t>
+          <t>34,17; 37,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,51; 36,22</t>
+          <t>33,52; 36,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,53; 36,13</t>
+          <t>34,59; 36,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,14; 40,78</t>
+          <t>39,15; 40,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38,35; 40,01</t>
+          <t>38,25; 39,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36,88; 38,58</t>
+          <t>36,89; 38,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,22; 38,45</t>
+          <t>37,25; 38,43</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>40,81</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>35,79</t>
+          <t>35,53</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,99</t>
+          <t>38,39</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,85; 42,67</t>
+          <t>40,76; 42,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,71; 42,58</t>
+          <t>40,8; 42,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,19; 41,37</t>
+          <t>39,09; 41,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,95; 40,8</t>
+          <t>39,98; 41,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,08; 41,95</t>
+          <t>38,11; 42,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,0; 37,45</t>
+          <t>34,09; 37,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,44; 36,77</t>
+          <t>33,38; 36,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,62; 36,79</t>
+          <t>34,67; 36,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40,25; 41,98</t>
+          <t>40,34; 42,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38,38; 40,21</t>
+          <t>38,42; 40,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,17; 39,06</t>
+          <t>37,12; 39,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,14; 38,46</t>
+          <t>37,77; 39,05</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40,66</t>
+          <t>40,59</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35,89</t>
+          <t>35,61</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38,72</t>
+          <t>38,53</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,21; 44,44</t>
+          <t>41,2; 44,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,06; 44,37</t>
+          <t>40,98; 44,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,77; 42,28</t>
+          <t>38,82; 42,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39,8; 41,5</t>
+          <t>39,69; 41,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,02; 39,47</t>
+          <t>34,02; 39,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,9; 41,93</t>
+          <t>36,77; 42,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,29; 37,07</t>
+          <t>32,3; 36,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,91; 36,8</t>
+          <t>34,58; 36,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,58; 42,37</t>
+          <t>39,63; 42,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40,51; 43,14</t>
+          <t>40,4; 43,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36,84; 39,63</t>
+          <t>36,9; 39,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,07; 39,36</t>
+          <t>37,79; 39,22</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39,21</t>
+          <t>39,32</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>35,13</t>
+          <t>34,92</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,2</t>
+          <t>37,21</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,1; 41,03</t>
+          <t>16,1; 42,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37,07; 41,91</t>
+          <t>37,21; 41,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,21; 42,05</t>
+          <t>24,13; 42,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,56; 38,77</t>
+          <t>29,27; 38,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,72; 45,91</t>
+          <t>20,58; 46,32</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,79; 37,29</t>
+          <t>16,16; 37,28</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,52; 40,04</t>
+          <t>24,54; 40,59</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>34,41; 39,41</t>
+          <t>34,44; 39,34</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34,67</t>
+          <t>34,88</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,67</t>
+          <t>34,88</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35,7</t>
+          <t>39,86</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>34,87</t>
+          <t>35,47</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>35,35</t>
+          <t>37,92</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>40,71; 41,65</t>
+          <t>40,67; 41,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40,76; 41,78</t>
+          <t>40,77; 41,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38,88; 40,07</t>
+          <t>38,87; 40,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,59; 39,87</t>
+          <t>39,41; 40,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>36,41; 37,96</t>
+          <t>36,34; 37,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,06; 36,56</t>
+          <t>35,09; 36,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,18; 35,67</t>
+          <t>34,11; 35,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,33; 35,79</t>
+          <t>34,96; 35,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39,34; 40,16</t>
+          <t>39,34; 40,18</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38,59; 39,51</t>
+          <t>38,6; 39,51</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37,06; 38,02</t>
+          <t>37,05; 38,01</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,34; 37,75</t>
+          <t>37,6; 38,23</t>
         </is>
       </c>
     </row>
